--- a/metrics/Global_Metrics_Ablation_Study_RHm.xlsx
+++ b/metrics/Global_Metrics_Ablation_Study_RHm.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U4"/>
+  <dimension ref="A1:AS4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -471,60 +471,180 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
+          <t>MAE_constant</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_constant</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_constant</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_constant</t>
+        </is>
+      </c>
+      <c r="N1" s="1" t="inlineStr">
+        <is>
+          <t>R2_constant</t>
+        </is>
+      </c>
+      <c r="O1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_constant</t>
+        </is>
+      </c>
+      <c r="P1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_constant</t>
+        </is>
+      </c>
+      <c r="Q1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_constant</t>
+        </is>
+      </c>
+      <c r="R1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_stepwise</t>
+        </is>
+      </c>
+      <c r="S1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_stepwise</t>
+        </is>
+      </c>
+      <c r="T1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_stepwise</t>
+        </is>
+      </c>
+      <c r="U1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_stepwise</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>R2_stepwise</t>
+        </is>
+      </c>
+      <c r="W1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_stepwise</t>
+        </is>
+      </c>
+      <c r="X1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_stepwise</t>
+        </is>
+      </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_stepwise</t>
+        </is>
+      </c>
+      <c r="Z1" s="1" t="inlineStr">
+        <is>
+          <t>MAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AA1" s="1" t="inlineStr">
+        <is>
+          <t>MedAE_dynamic</t>
+        </is>
+      </c>
+      <c r="AB1" s="1" t="inlineStr">
+        <is>
+          <t>MSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AC1" s="1" t="inlineStr">
+        <is>
+          <t>RMSE_dynamic</t>
+        </is>
+      </c>
+      <c r="AD1" s="1" t="inlineStr">
+        <is>
+          <t>R2_dynamic</t>
+        </is>
+      </c>
+      <c r="AE1" s="1" t="inlineStr">
+        <is>
+          <t>Pearson_dynamic</t>
+        </is>
+      </c>
+      <c r="AF1" s="1" t="inlineStr">
+        <is>
+          <t>Spearman_dynamic</t>
+        </is>
+      </c>
+      <c r="AG1" s="1" t="inlineStr">
+        <is>
+          <t>Kendall_dynamic</t>
+        </is>
+      </c>
+      <c r="AH1" s="1" t="inlineStr">
+        <is>
           <t>Int_Conf_R2</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="AI1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_RMSE</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="AJ1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Pearson</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="AK1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Spearman</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="AL1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_Kendall</t>
         </is>
       </c>
-      <c r="O1" s="1" t="inlineStr">
+      <c r="AM1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MAE</t>
         </is>
       </c>
-      <c r="P1" s="1" t="inlineStr">
+      <c r="AN1" s="1" t="inlineStr">
         <is>
           <t>Int_Conf_MedAE</t>
         </is>
       </c>
-      <c r="Q1" s="1" t="inlineStr">
+      <c r="AO1" s="1" t="inlineStr">
         <is>
           <t>Target</t>
         </is>
       </c>
-      <c r="R1" s="1" t="inlineStr">
+      <c r="AP1" s="1" t="inlineStr">
         <is>
           <t>Model</t>
         </is>
       </c>
-      <c r="S1" s="1" t="inlineStr">
+      <c r="AQ1" s="1" t="inlineStr">
         <is>
           <t>Lag</t>
         </is>
       </c>
-      <c r="T1" s="1" t="inlineStr">
+      <c r="AR1" s="1" t="inlineStr">
         <is>
           <t>Max_Step</t>
         </is>
       </c>
-      <c r="U1" s="1" t="inlineStr">
+      <c r="AS1" s="1" t="inlineStr">
         <is>
           <t>Pred_Step</t>
         </is>
@@ -535,67 +655,139 @@
         <v>0</v>
       </c>
       <c r="B2" t="n">
-        <v>2.638847774345717</v>
+        <v>2.446608884430923</v>
       </c>
       <c r="C2" t="n">
-        <v>2.492792861735929</v>
+        <v>2.279726660734038</v>
       </c>
       <c r="D2" t="n">
-        <v>9.346537217006073</v>
+        <v>8.201827025617826</v>
       </c>
       <c r="E2" t="n">
-        <v>3.057210692282439</v>
+        <v>2.863883207398274</v>
       </c>
       <c r="F2" t="n">
-        <v>0.8827753645629336</v>
+        <v>0.9078794131405356</v>
       </c>
       <c r="G2" t="n">
-        <v>0.9396152456521601</v>
+        <v>0.9528601306701922</v>
       </c>
       <c r="H2" t="n">
-        <v>0.9397380853952529</v>
+        <v>0.9526016791988848</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7949417462877139</v>
+        <v>0.8219367075890635</v>
       </c>
       <c r="J2" t="n">
-        <v>0.01013156346798605</v>
+        <v>3.136254752178689</v>
       </c>
       <c r="K2" t="n">
-        <v>0.1246737254678423</v>
+        <v>3.234596735664979</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4723646513628096</v>
+        <v>12.01400655867301</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4740704558521048</v>
+        <v>3.466122698156112</v>
       </c>
       <c r="N2" t="n">
-        <v>0.3980819650089913</v>
+        <v>0.8709289655191286</v>
       </c>
       <c r="O2" t="n">
-        <v>0.1128154496448159</v>
+        <v>0.978857165090296</v>
       </c>
       <c r="P2" t="n">
-        <v>0.1148322174120913</v>
-      </c>
-      <c r="Q2" t="inlineStr">
+        <v>0.984762456125378</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>0.9149970544971406</v>
+      </c>
+      <c r="R2" t="n">
+        <v>2.274285798810852</v>
+      </c>
+      <c r="S2" t="n">
+        <v>2.357590483625861</v>
+      </c>
+      <c r="T2" t="n">
+        <v>6.194324000802114</v>
+      </c>
+      <c r="U2" t="n">
+        <v>2.488839890551844</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.9163792391379484</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.9577275708649376</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.9520324889349692</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.8168967123060404</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>2.298367925618884</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>1.95945698359499</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>8.010127177124465</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>2.830216807441519</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>0.9046554528113395</v>
+      </c>
+      <c r="AE2" t="n">
+        <v>0.959499527791546</v>
+      </c>
+      <c r="AF2" t="n">
+        <v>0.9606624518237088</v>
+      </c>
+      <c r="AG2" t="n">
+        <v>0.8415364645997634</v>
+      </c>
+      <c r="AH2" t="n">
+        <v>0.01859806584557555</v>
+      </c>
+      <c r="AI2" t="n">
+        <v>0.22900008783561</v>
+      </c>
+      <c r="AJ2" t="n">
+        <v>0.009869542905488637</v>
+      </c>
+      <c r="AK2" t="n">
+        <v>0.01186406989562944</v>
+      </c>
+      <c r="AL2" t="n">
+        <v>0.02301873766517137</v>
+      </c>
+      <c r="AM2" t="n">
+        <v>0.2050603657878318</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>0.1872403190159884</v>
+      </c>
+      <c r="AO2" t="inlineStr">
         <is>
           <t>RSL</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="AP2" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S2" t="n">
+      <c r="AQ2" t="n">
         <v>3</v>
       </c>
-      <c r="T2" t="n">
+      <c r="AR2" t="n">
         <v>1</v>
       </c>
-      <c r="U2" t="n">
+      <c r="AS2" t="n">
         <v>1</v>
       </c>
     </row>
@@ -604,67 +796,139 @@
         <v>1</v>
       </c>
       <c r="B3" t="n">
-        <v>0.3299817711194091</v>
+        <v>0.3472888138072268</v>
       </c>
       <c r="C3" t="n">
-        <v>0.2015815664837233</v>
+        <v>0.2369941224017217</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2245493977332884</v>
+        <v>0.2429538028740419</v>
       </c>
       <c r="E3" t="n">
-        <v>0.4738664344868588</v>
+        <v>0.492903441734831</v>
       </c>
       <c r="F3" t="n">
-        <v>0.9599534239370908</v>
+        <v>0.961237719562354</v>
       </c>
       <c r="G3" t="n">
-        <v>0.9808542236187824</v>
+        <v>0.9820821375915642</v>
       </c>
       <c r="H3" t="n">
-        <v>0.9857765866313875</v>
+        <v>0.9853548332833489</v>
       </c>
       <c r="I3" t="n">
-        <v>0.9005565618269536</v>
+        <v>0.8987707672850892</v>
       </c>
       <c r="J3" t="n">
-        <v>0.00639863206931629</v>
+        <v>0.2711879445485695</v>
       </c>
       <c r="K3" t="n">
-        <v>0.03669610249836824</v>
+        <v>0.2533818891183151</v>
       </c>
       <c r="L3" t="n">
-        <v>0.4910900423111912</v>
+        <v>0.1061499394190384</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4914363211695575</v>
+        <v>0.3258065981821706</v>
       </c>
       <c r="N3" t="n">
-        <v>0.4450930796681287</v>
+        <v>0.9809584946303236</v>
       </c>
       <c r="O3" t="n">
-        <v>0.02974291055383813</v>
+        <v>0.9911912920844584</v>
       </c>
       <c r="P3" t="n">
-        <v>0.02565837091855531</v>
-      </c>
-      <c r="Q3" t="inlineStr">
+        <v>0.9892140198595583</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>0.9225921554876131</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.2140310314957662</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.1265123566647718</v>
+      </c>
+      <c r="T3" t="n">
+        <v>0.09724848147502371</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.3118468878713137</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.9671098125006803</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.9891140587847069</v>
+      </c>
+      <c r="X3" t="n">
+        <v>0.9872898608327149</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>0.9079602691743509</v>
+      </c>
+      <c r="Z3" t="n">
+        <v>0.4542557441692607</v>
+      </c>
+      <c r="AA3" t="n">
+        <v>0.3610770641969285</v>
+      </c>
+      <c r="AB3" t="n">
+        <v>0.3794013494256904</v>
+      </c>
+      <c r="AC3" t="n">
+        <v>0.6159556391702981</v>
+      </c>
+      <c r="AD3" t="n">
+        <v>0.9454700038763624</v>
+      </c>
+      <c r="AE3" t="n">
+        <v>0.9815067200093494</v>
+      </c>
+      <c r="AF3" t="n">
+        <v>0.9874491123727208</v>
+      </c>
+      <c r="AG3" t="n">
+        <v>0.9070855577991779</v>
+      </c>
+      <c r="AH3" t="n">
+        <v>0.008184002171618576</v>
+      </c>
+      <c r="AI3" t="n">
+        <v>0.05252597724564406</v>
+      </c>
+      <c r="AJ3" t="n">
+        <v>0.003124155779649695</v>
+      </c>
+      <c r="AK3" t="n">
+        <v>0.004782179976794476</v>
+      </c>
+      <c r="AL3" t="n">
+        <v>0.01387770119220127</v>
+      </c>
+      <c r="AM3" t="n">
+        <v>0.0394262674874572</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>0.06116821293482287</v>
+      </c>
+      <c r="AO3" t="inlineStr">
         <is>
           <t>WL</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="AP3" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S3" t="n">
+      <c r="AQ3" t="n">
         <v>3</v>
       </c>
-      <c r="T3" t="n">
+      <c r="AR3" t="n">
         <v>1</v>
       </c>
-      <c r="U3" t="n">
+      <c r="AS3" t="n">
         <v>1</v>
       </c>
     </row>
@@ -673,67 +937,139 @@
         <v>2</v>
       </c>
       <c r="B4" t="n">
-        <v>1.062171564656967</v>
+        <v>1.089367352260461</v>
       </c>
       <c r="C4" t="n">
-        <v>0.6032990806600448</v>
+        <v>0.7092836680775392</v>
       </c>
       <c r="D4" t="n">
-        <v>2.546993857633856</v>
+        <v>2.637258184573435</v>
       </c>
       <c r="E4" t="n">
-        <v>1.595930405009522</v>
+        <v>1.623963726372432</v>
       </c>
       <c r="F4" t="n">
-        <v>0.9597808064947267</v>
+        <v>0.962695881052922</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9796935939308851</v>
+        <v>0.9813407450073064</v>
       </c>
       <c r="H4" t="n">
-        <v>0.9784208908210669</v>
+        <v>0.9766474972823265</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8815258609474896</v>
+        <v>0.8792148570875927</v>
       </c>
       <c r="J4" t="n">
-        <v>0.007196225191687389</v>
+        <v>1.067366531858883</v>
       </c>
       <c r="K4" t="n">
-        <v>0.150167670846829</v>
+        <v>0.8502619554409826</v>
       </c>
       <c r="L4" t="n">
-        <v>0.4913192861756201</v>
+        <v>1.852606807364717</v>
       </c>
       <c r="M4" t="n">
-        <v>0.4877864182863721</v>
+        <v>1.361104994981915</v>
       </c>
       <c r="N4" t="n">
-        <v>0.4366755740799874</v>
+        <v>0.977998297816742</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1064802876169258</v>
+        <v>0.9911295374792453</v>
       </c>
       <c r="P4" t="n">
-        <v>0.07885541935852697</v>
-      </c>
-      <c r="Q4" t="inlineStr">
+        <v>0.9872460379087358</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>0.9291046014397268</v>
+      </c>
+      <c r="R4" t="n">
+        <v>1.294456135285142</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.7360156097932913</v>
+      </c>
+      <c r="T4" t="n">
+        <v>4.207488188005653</v>
+      </c>
+      <c r="U4" t="n">
+        <v>2.051216270412668</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.8968823685012912</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.960307745546308</v>
+      </c>
+      <c r="X4" t="n">
+        <v>0.9507013207598671</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>0.8311627876146804</v>
+      </c>
+      <c r="Z4" t="n">
+        <v>0.9753313499455234</v>
+      </c>
+      <c r="AA4" t="n">
+        <v>0.6311587756394768</v>
+      </c>
+      <c r="AB4" t="n">
+        <v>1.988234220524377</v>
+      </c>
+      <c r="AC4" t="n">
+        <v>1.410047595127334</v>
+      </c>
+      <c r="AD4" t="n">
+        <v>0.9745394004593533</v>
+      </c>
+      <c r="AE4" t="n">
+        <v>0.9875914553375708</v>
+      </c>
+      <c r="AF4" t="n">
+        <v>0.9839761907389161</v>
+      </c>
+      <c r="AG4" t="n">
+        <v>0.9004660017004785</v>
+      </c>
+      <c r="AH4" t="n">
+        <v>0.01124811528158448</v>
+      </c>
+      <c r="AI4" t="n">
+        <v>0.2411438998206802</v>
+      </c>
+      <c r="AJ4" t="n">
+        <v>0.005417291175988714</v>
+      </c>
+      <c r="AK4" t="n">
+        <v>0.006542468245222921</v>
+      </c>
+      <c r="AL4" t="n">
+        <v>0.01526658172415074</v>
+      </c>
+      <c r="AM4" t="n">
+        <v>0.1417036368502227</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>0.09710663595309049</v>
+      </c>
+      <c r="AO4" t="inlineStr">
         <is>
           <t>DI</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="AP4" t="inlineStr">
         <is>
           <t>RF</t>
         </is>
       </c>
-      <c r="S4" t="n">
+      <c r="AQ4" t="n">
         <v>3</v>
       </c>
-      <c r="T4" t="n">
+      <c r="AR4" t="n">
         <v>1</v>
       </c>
-      <c r="U4" t="n">
+      <c r="AS4" t="n">
         <v>1</v>
       </c>
     </row>
